--- a/levenshtein/levenshtein_words_toneless.xlsx
+++ b/levenshtein/levenshtein_words_toneless.xlsx
@@ -7945,7 +7945,7 @@
     <t>kʰəɕitʰəu</t>
   </si>
   <si>
-    <t>tʰueitu+Hpɔ</t>
+    <t>tʰueitupɔ</t>
   </si>
   <si>
     <t>mɐ</t>
